--- a/data/trans_camb/IP04D$aparatos-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$aparatos-Provincia-trans_camb.xlsx
@@ -581,7 +581,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-63,79; -38,76</t>
+          <t>-64,35; -38,63</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-49,7; -20,59</t>
+          <t>-50,8; -22,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-45,52; -20,36</t>
+          <t>-47,13; -19,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-29,2; -2,05</t>
+          <t>-30,09; -1,92</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-50,55; -31,02</t>
+          <t>-51,02; -32,65</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,93; -13,98</t>
+          <t>-35,58; -15,18</t>
         </is>
       </c>
     </row>
@@ -705,39 +705,39 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-90,66; -67,66</t>
+          <t>-90,3; -67,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-71,31; -36,9</t>
+          <t>-71,5; -37,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-82,15; -46,57</t>
+          <t>-82,78; -46,67</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-53,09; -2,84</t>
+          <t>-54,75; -4,24</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-83,38; -62,73</t>
+          <t>-84,51; -63,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-57,8; -27,37</t>
+          <t>-58,73; -29,56</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-41,16; -18,11</t>
+          <t>-41,8; -20,3</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,3; 30,88</t>
+          <t>11,41; 31,27</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-41,9; -21,69</t>
+          <t>-42,55; -22,12</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>11,48; 30,09</t>
+          <t>10,77; 29,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-38,59; -24,15</t>
+          <t>-39,33; -24,03</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,8; 28,52</t>
+          <t>13,5; 26,83</t>
         </is>
       </c>
     </row>
@@ -861,39 +861,39 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-56,23; -29,23</t>
+          <t>-56,28; -31,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>16,19; 49,99</t>
+          <t>15,07; 49,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-60,42; -36,41</t>
+          <t>-61,33; -37,04</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,62; 50,79</t>
+          <t>15,76; 50,42</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,69; -38,38</t>
+          <t>-55,36; -36,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,91; 45,18</t>
+          <t>18,94; 42,55</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,0; 14,32</t>
+          <t>-10,64; 13,04</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-22,6; 3,46</t>
+          <t>-22,55; 2,69</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-11,2; 12,36</t>
+          <t>-9,96; 12,09</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-28,88; -3,53</t>
+          <t>-29,37; -3,48</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,55; 9,46</t>
+          <t>-7,8; 9,1</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,95; -3,32</t>
+          <t>-21,38; -3,74</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,75; 21,69</t>
+          <t>-13,43; 19,15</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-28,28; 5,13</t>
+          <t>-28,61; 3,46</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-13,55; 17,09</t>
+          <t>-11,7; 17,31</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-35,21; -4,87</t>
+          <t>-35,47; -4,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-9,56; 13,25</t>
+          <t>-9,87; 12,58</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-27,5; -4,61</t>
+          <t>-26,86; -5,23</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,37; 17,68</t>
+          <t>-9,11; 16,56</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-34,15; -5,55</t>
+          <t>-33,93; -6,27</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,38; 12,61</t>
+          <t>-13,56; 12,43</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-45,12; -11,44</t>
+          <t>-43,47; -10,38</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,87; 11,54</t>
+          <t>-7,08; 11,33</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-35,43; -12,15</t>
+          <t>-35,21; -13,56</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,32; 34,9</t>
+          <t>-14,2; 32,4</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-55,1; -11,68</t>
+          <t>-53,67; -11,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-19,49; 22,53</t>
+          <t>-20,37; 22,97</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-69,36; -21,1</t>
+          <t>-68,26; -19,25</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,27; 20,46</t>
+          <t>-11,28; 21,44</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-56,57; -22,85</t>
+          <t>-57,17; -23,89</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12,04; 41,61</t>
+          <t>12,61; 42,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>25,12; 50,29</t>
+          <t>24,0; 49,85</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>16,26; 45,84</t>
+          <t>18,75; 47,63</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30,97; 55,74</t>
+          <t>31,36; 56,4</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18,99; 40,71</t>
+          <t>20,31; 40,78</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,0; 49,44</t>
+          <t>31,58; 48,9</t>
         </is>
       </c>
     </row>
@@ -1329,39 +1329,39 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>16,94; 80,85</t>
+          <t>17,94; 87,37</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>34,78; 108,06</t>
+          <t>33,76; 103,69</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>26,21; 102,57</t>
+          <t>28,9; 109,67</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44,86; 125,94</t>
+          <t>45,69; 129,37</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>28,71; 81,14</t>
+          <t>30,51; 77,67</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>45,0; 97,4</t>
+          <t>47,77; 97,01</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1409,32 +1409,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-61,01; -34,62</t>
+          <t>-61,46; -34,85</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-36,29; -6,89</t>
+          <t>-38,37; -7,99</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-66,0; -39,38</t>
+          <t>-65,98; -39,96</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-48,92; -20,24</t>
+          <t>-48,13; -21,17</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-61,15; -41,92</t>
+          <t>-61,55; -42,0</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-39,79; -18,47</t>
+          <t>-38,69; -18,7</t>
         </is>
       </c>
     </row>
@@ -1485,39 +1485,39 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-84,63; -57,13</t>
+          <t>-84,39; -57,51</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-50,22; -11,3</t>
+          <t>-52,66; -14,0</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-81,93; -55,97</t>
+          <t>-82,72; -57,47</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-60,3; -28,83</t>
+          <t>-59,83; -30,2</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-80,34; -61,47</t>
+          <t>-81,05; -61,96</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-52,79; -27,67</t>
+          <t>-51,88; -28,39</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1565,32 +1565,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-34,77; -16,36</t>
+          <t>-35,55; -16,59</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-55,18; -34,97</t>
+          <t>-54,28; -34,06</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-31,07; -12,65</t>
+          <t>-31,77; -13,97</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-62,69; -45,18</t>
+          <t>-62,56; -45,53</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-30,77; -18,1</t>
+          <t>-31,31; -17,87</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-56,76; -43,4</t>
+          <t>-56,87; -43,31</t>
         </is>
       </c>
     </row>
@@ -1641,32 +1641,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-44,75; -23,36</t>
+          <t>-44,87; -23,68</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-69,03; -47,0</t>
+          <t>-69,6; -47,35</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-39,85; -17,78</t>
+          <t>-41,26; -19,32</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-81,25; -63,35</t>
+          <t>-81,04; -62,72</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-39,74; -25,14</t>
+          <t>-40,12; -24,29</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-73,86; -59,7</t>
+          <t>-74,36; -59,71</t>
         </is>
       </c>
     </row>
@@ -1721,32 +1721,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>3,81; 20,65</t>
+          <t>4,18; 20,58</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>35,16; 49,62</t>
+          <t>35,48; 49,55</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>14,26; 30,6</t>
+          <t>12,5; 30,32</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>43,12; 56,46</t>
+          <t>43,55; 57,74</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>11,24; 23,24</t>
+          <t>11,72; 23,23</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>41,68; 51,08</t>
+          <t>41,54; 51,85</t>
         </is>
       </c>
     </row>
@@ -1797,32 +1797,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>7,48; 45,67</t>
+          <t>7,68; 45,57</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>61,87; 110,41</t>
+          <t>63,19; 110,64</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>28,64; 77,75</t>
+          <t>26,19; 76,88</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>87,9; 149,03</t>
+          <t>87,01; 149,62</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>22,21; 53,29</t>
+          <t>23,45; 53,72</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>80,71; 118,66</t>
+          <t>81,29; 119,25</t>
         </is>
       </c>
     </row>
@@ -1877,32 +1877,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-16,72; -7,9</t>
+          <t>-16,5; -7,96</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-6,56; 4,09</t>
+          <t>-6,65; 4,3</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-13,06; -4,8</t>
+          <t>-13,46; -5,19</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 1,46</t>
+          <t>-8,36; 1,36</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-13,92; -7,73</t>
+          <t>-13,89; -7,73</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-6,15; 0,87</t>
+          <t>-6,69; 0,75</t>
         </is>
       </c>
     </row>
@@ -1953,32 +1953,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-25,27; -12,66</t>
+          <t>-24,84; -12,81</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-9,94; 6,5</t>
+          <t>-10,04; 7,01</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-20,56; -8,01</t>
+          <t>-21,1; -8,56</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-12,65; 2,47</t>
+          <t>-13,15; 1,95</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-21,54; -12,49</t>
+          <t>-21,77; -12,72</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-9,68; 1,42</t>
+          <t>-10,34; 1,25</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$aparatos-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$aparatos-Provincia-trans_camb.xlsx
@@ -629,32 +629,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-64,35; -38,63</t>
+          <t>-64,2; -40,03</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-50,8; -22,19</t>
+          <t>-50,03; -21,64</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-47,13; -19,72</t>
+          <t>-44,41; -19,14</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-30,09; -1,92</t>
+          <t>-30,3; -1,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-51,02; -32,65</t>
+          <t>-50,96; -32,91</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-35,58; -15,18</t>
+          <t>-34,47; -14,54</t>
         </is>
       </c>
     </row>
@@ -705,32 +705,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-90,3; -67,47</t>
+          <t>-90,01; -68,08</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-71,5; -37,06</t>
+          <t>-71,12; -37,83</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-82,78; -46,67</t>
+          <t>-80,94; -44,72</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-54,75; -4,24</t>
+          <t>-54,89; -2,54</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-84,51; -63,71</t>
+          <t>-82,67; -63,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-58,73; -29,56</t>
+          <t>-57,39; -29,35</t>
         </is>
       </c>
     </row>
@@ -785,32 +785,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-41,8; -20,3</t>
+          <t>-41,21; -19,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>11,41; 31,27</t>
+          <t>12,38; 31,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-42,55; -22,12</t>
+          <t>-43,35; -22,64</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,77; 29,42</t>
+          <t>10,2; 30,18</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-39,33; -24,03</t>
+          <t>-38,83; -23,63</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,5; 26,83</t>
+          <t>14,46; 28,43</t>
         </is>
       </c>
     </row>
@@ -861,32 +861,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-56,28; -31,3</t>
+          <t>-56,15; -29,63</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,07; 49,57</t>
+          <t>15,85; 48,96</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-61,33; -37,04</t>
+          <t>-61,46; -36,94</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,76; 50,42</t>
+          <t>14,26; 51,2</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,36; -36,87</t>
+          <t>-55,31; -37,02</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>18,94; 42,55</t>
+          <t>20,21; 45,22</t>
         </is>
       </c>
     </row>
@@ -941,32 +941,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-10,64; 13,04</t>
+          <t>-11,95; 12,6</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-22,55; 2,69</t>
+          <t>-22,01; 3,62</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-9,96; 12,09</t>
+          <t>-10,06; 12,31</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-29,37; -3,48</t>
+          <t>-27,58; -3,37</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-7,8; 9,1</t>
+          <t>-6,87; 9,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-21,38; -3,74</t>
+          <t>-20,94; -3,43</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1017,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-13,43; 19,15</t>
+          <t>-15,01; 18,52</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-28,61; 3,46</t>
+          <t>-27,44; 5,23</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-11,7; 17,31</t>
+          <t>-12,14; 17,14</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-35,47; -4,98</t>
+          <t>-33,73; -4,56</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-9,87; 12,58</t>
+          <t>-8,46; 13,01</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-26,86; -5,23</t>
+          <t>-26,81; -5,02</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1097,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-9,11; 16,56</t>
+          <t>-8,22; 16,58</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-33,93; -6,27</t>
+          <t>-32,41; -5,33</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-13,56; 12,43</t>
+          <t>-12,66; 12,6</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-43,47; -10,38</t>
+          <t>-44,89; -11,48</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-7,08; 11,33</t>
+          <t>-8,17; 10,76</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-35,21; -13,56</t>
+          <t>-35,79; -12,93</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1173,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-14,2; 32,4</t>
+          <t>-12,44; 33,51</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-53,67; -11,34</t>
+          <t>-52,61; -11,14</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-20,37; 22,97</t>
+          <t>-18,59; 23,0</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-68,26; -19,25</t>
+          <t>-68,61; -19,83</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-11,28; 21,44</t>
+          <t>-12,81; 19,62</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-57,17; -23,89</t>
+          <t>-57,29; -22,65</t>
         </is>
       </c>
     </row>
@@ -1253,32 +1253,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12,61; 42,6</t>
+          <t>12,64; 42,78</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>24,0; 49,85</t>
+          <t>24,92; 49,96</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18,75; 47,63</t>
+          <t>18,66; 47,5</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>31,36; 56,4</t>
+          <t>32,1; 55,75</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>20,31; 40,78</t>
+          <t>19,2; 39,87</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,58; 48,9</t>
+          <t>31,79; 49,12</t>
         </is>
       </c>
     </row>
@@ -1329,32 +1329,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>17,94; 87,37</t>
+          <t>18,22; 86,34</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>33,76; 103,69</t>
+          <t>34,52; 101,8</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28,9; 109,67</t>
+          <t>28,67; 104,94</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>45,69; 129,37</t>
+          <t>47,27; 125,98</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>30,51; 77,67</t>
+          <t>28,43; 77,81</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,77; 97,01</t>
+          <t>47,6; 98,73</t>
         </is>
       </c>
     </row>
@@ -1409,32 +1409,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-61,46; -34,85</t>
+          <t>-61,26; -34,51</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-38,37; -7,99</t>
+          <t>-36,83; -7,0</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-65,98; -39,96</t>
+          <t>-66,73; -40,06</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-48,13; -21,17</t>
+          <t>-49,03; -22,2</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-61,55; -42,0</t>
+          <t>-60,72; -42,25</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-38,69; -18,7</t>
+          <t>-39,92; -18,13</t>
         </is>
       </c>
     </row>
@@ -1485,32 +1485,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-84,39; -57,51</t>
+          <t>-84,02; -56,28</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-52,66; -14,0</t>
+          <t>-51,54; -12,04</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-82,72; -57,47</t>
+          <t>-83,09; -55,99</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-59,83; -30,2</t>
+          <t>-61,53; -31,41</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-81,05; -61,96</t>
+          <t>-79,89; -61,27</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-51,88; -28,39</t>
+          <t>-52,65; -27,81</t>
         </is>
       </c>
     </row>
@@ -1565,32 +1565,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-35,55; -16,59</t>
+          <t>-34,82; -16,43</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-54,28; -34,06</t>
+          <t>-54,6; -35,06</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-31,77; -13,97</t>
+          <t>-31,33; -12,86</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-62,56; -45,53</t>
+          <t>-62,29; -45,17</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-31,31; -17,87</t>
+          <t>-30,64; -16,83</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-56,87; -43,31</t>
+          <t>-56,75; -43,3</t>
         </is>
       </c>
     </row>
@@ -1641,32 +1641,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-44,87; -23,68</t>
+          <t>-45,71; -23,87</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-69,6; -47,35</t>
+          <t>-69,26; -48,29</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-41,26; -19,32</t>
+          <t>-40,47; -18,15</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-81,04; -62,72</t>
+          <t>-80,93; -62,05</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-40,12; -24,29</t>
+          <t>-39,52; -23,05</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-74,36; -59,71</t>
+          <t>-73,87; -59,0</t>
         </is>
       </c>
     </row>
@@ -1721,32 +1721,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>4,18; 20,58</t>
+          <t>4,04; 21,13</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>35,48; 49,55</t>
+          <t>35,72; 49,56</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>12,5; 30,32</t>
+          <t>12,9; 30,36</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>43,55; 57,74</t>
+          <t>42,92; 56,47</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>11,72; 23,23</t>
+          <t>10,66; 23,03</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>41,54; 51,85</t>
+          <t>40,99; 51,45</t>
         </is>
       </c>
     </row>
@@ -1797,32 +1797,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>7,68; 45,57</t>
+          <t>7,76; 46,49</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>63,19; 110,64</t>
+          <t>64,33; 110,44</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>26,19; 76,88</t>
+          <t>27,22; 78,22</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>87,01; 149,62</t>
+          <t>86,18; 148,1</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>23,45; 53,72</t>
+          <t>21,7; 52,75</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>81,29; 119,25</t>
+          <t>79,68; 119,52</t>
         </is>
       </c>
     </row>
@@ -1877,32 +1877,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-16,5; -7,96</t>
+          <t>-16,94; -8,03</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 4,3</t>
+          <t>-6,69; 4,45</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-13,46; -5,19</t>
+          <t>-13,31; -5,0</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 1,36</t>
+          <t>-8,57; 1,5</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-13,89; -7,73</t>
+          <t>-13,77; -7,92</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 0,75</t>
+          <t>-5,76; 1,24</t>
         </is>
       </c>
     </row>
@@ -1953,32 +1953,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-24,84; -12,81</t>
+          <t>-25,55; -12,95</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-10,04; 7,01</t>
+          <t>-10,29; 6,93</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-21,1; -8,56</t>
+          <t>-20,81; -8,27</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 1,95</t>
+          <t>-13,79; 2,36</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-21,77; -12,72</t>
+          <t>-21,45; -12,79</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-10,34; 1,25</t>
+          <t>-9,08; 1,99</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP04D$aparatos-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP04D$aparatos-Provincia-trans_camb.xlsx
@@ -511,19 +511,21 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="n">
-        <v/>
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Población que no dispone de instalación de calefacción en su vivienda pero sí tiene aparatos de calefacción</t>
+        </is>
       </c>
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -591,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>-32,01</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>-14,06</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>-52,27</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-36,18</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>-32,01</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-15,57</t>
+          <t>-30,78</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -616,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-25,22</t>
+          <t>-21,85</t>
         </is>
       </c>
     </row>
@@ -629,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-64,2; -40,03</t>
+          <t>-45,52; -20,36</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-50,03; -21,64</t>
+          <t>-28,27; -1,12</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-44,41; -19,14</t>
+          <t>-63,79; -38,76</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-30,3; -1,68</t>
+          <t>-42,94; -14,98</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-50,96; -32,91</t>
+          <t>-50,55; -31,02</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,47; -14,54</t>
+          <t>-31,78; -10,97</t>
         </is>
       </c>
     </row>
@@ -667,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>-67,3%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>-29,56%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>-80,97%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-56,04%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>-67,3%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>-32,73%</t>
+          <t>-47,68%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -692,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-45,45%</t>
+          <t>-39,38%</t>
         </is>
       </c>
     </row>
@@ -705,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-90,01; -68,08</t>
+          <t>-82,15; -46,57</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-71,12; -37,83</t>
+          <t>-50,46; 0,57</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-80,94; -44,72</t>
+          <t>-90,66; -67,66</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-54,89; -2,54</t>
+          <t>-62,42; -27,21</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-82,67; -63,33</t>
+          <t>-83,38; -62,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-57,39; -29,35</t>
+          <t>-52,1; -21,78</t>
         </is>
       </c>
     </row>
@@ -747,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>-32,46</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>20,88</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>-30,48</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>21,59</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>-32,46</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>20,9</t>
+          <t>19,66</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -772,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,3</t>
+          <t>20,23</t>
         </is>
       </c>
     </row>
@@ -785,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-41,21; -19,34</t>
+          <t>-41,9; -21,69</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,38; 31,12</t>
+          <t>11,1; 30,12</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-43,35; -22,64</t>
+          <t>-41,16; -18,11</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10,2; 30,18</t>
+          <t>10,28; 28,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-38,83; -23,63</t>
+          <t>-38,59; -24,15</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>14,46; 28,43</t>
+          <t>13,86; 26,76</t>
         </is>
       </c>
     </row>
@@ -823,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>-49,5%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>31,84%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>-43,83%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>31,04%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-49,5%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>31,87%</t>
+          <t>28,27%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -848,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>31,55%</t>
+          <t>29,97%</t>
         </is>
       </c>
     </row>
@@ -861,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-56,15; -29,63</t>
+          <t>-60,42; -36,41</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>15,85; 48,96</t>
+          <t>15,59; 50,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-61,46; -36,94</t>
+          <t>-56,23; -29,23</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,26; 51,2</t>
+          <t>13,48; 45,91</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-55,31; -37,02</t>
+          <t>-55,69; -38,38</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,21; 45,22</t>
+          <t>19,48; 42,68</t>
         </is>
       </c>
     </row>
@@ -903,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>0,95</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>-15,96</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>0,93</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-9,32</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>0,95</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-15,49</t>
+          <t>-9,25</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -928,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-12,54</t>
+          <t>-12,68</t>
         </is>
       </c>
     </row>
@@ -941,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-11,95; 12,6</t>
+          <t>-11,2; 12,36</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-22,01; 3,62</t>
+          <t>-29,51; -4,06</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-10,06; 12,31</t>
+          <t>-11,0; 14,32</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-27,58; -3,37</t>
+          <t>-22,36; 3,46</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-6,87; 9,55</t>
+          <t>-7,55; 9,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-20,94; -3,43</t>
+          <t>-22,04; -3,53</t>
         </is>
       </c>
     </row>
@@ -979,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1,21%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>-20,44%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>1,25%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>-12,5%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>1,21%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>-19,84%</t>
+          <t>-12,41%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1004,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-16,42%</t>
+          <t>-16,61%</t>
         </is>
       </c>
     </row>
@@ -1017,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-15,01; 18,52</t>
+          <t>-13,55; 17,09</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-27,44; 5,23</t>
+          <t>-35,72; -5,73</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-12,14; 17,14</t>
+          <t>-13,75; 21,69</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-33,73; -4,56</t>
+          <t>-28,37; 4,87</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-8,46; 13,01</t>
+          <t>-9,56; 13,25</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-26,81; -5,02</t>
+          <t>-27,65; -4,83</t>
         </is>
       </c>
     </row>
@@ -1059,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>-0,31</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>-27,35</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>4,31</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>-20,05</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>-0,31</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>-27,51</t>
+          <t>-21,92</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1084,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-23,95</t>
+          <t>-24,7</t>
         </is>
       </c>
     </row>
@@ -1097,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-8,22; 16,58</t>
+          <t>-13,38; 12,61</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-32,41; -5,33</t>
+          <t>-44,6; -10,1</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-12,66; 12,6</t>
+          <t>-9,37; 17,68</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-44,89; -11,48</t>
+          <t>-35,92; -7,72</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-8,17; 10,76</t>
+          <t>-7,87; 11,54</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-35,79; -12,93</t>
+          <t>-35,93; -13,21</t>
         </is>
       </c>
     </row>
@@ -1135,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>-0,52%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>-44,91%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>7,5%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>-34,88%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>-0,52%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>-45,18%</t>
+          <t>-38,13%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1160,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-40,44%</t>
+          <t>-41,69%</t>
         </is>
       </c>
     </row>
@@ -1173,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-12,44; 33,51</t>
+          <t>-19,49; 22,53</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-52,61; -11,14</t>
+          <t>-67,79; -20,11</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-18,59; 23,0</t>
+          <t>-14,32; 34,9</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-68,61; -19,83</t>
+          <t>-57,7; -15,77</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-12,81; 19,62</t>
+          <t>-12,27; 20,46</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-57,29; -22,65</t>
+          <t>-57,23; -24,25</t>
         </is>
       </c>
     </row>
@@ -1215,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>32,67</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>43,2</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>27,58</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>36,68</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>32,67</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>43,2</t>
+          <t>36,73</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1253,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>12,64; 42,78</t>
+          <t>16,26; 45,84</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>24,92; 49,96</t>
+          <t>30,97; 55,74</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>18,66; 47,5</t>
+          <t>12,04; 41,61</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>32,1; 55,75</t>
+          <t>25,31; 50,32</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>19,2; 39,87</t>
+          <t>18,99; 40,71</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>31,79; 49,12</t>
+          <t>31,02; 49,46</t>
         </is>
       </c>
     </row>
@@ -1291,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>57,51%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>76,05%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>44,69%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>59,42%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>57,51%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>76,05%</t>
+          <t>59,51%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1329,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>18,22; 86,34</t>
+          <t>26,21; 102,57</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>34,52; 101,8</t>
+          <t>44,86; 125,94</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>28,67; 104,94</t>
+          <t>16,94; 80,85</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>47,27; 125,98</t>
+          <t>34,82; 107,77</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>28,43; 77,81</t>
+          <t>28,71; 81,14</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>47,6; 98,73</t>
+          <t>45,0; 97,36</t>
         </is>
       </c>
     </row>
@@ -1371,22 +1373,22 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>-54,67</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>-34,32</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
           <t>-48,84</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>-22,96</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>-54,67</t>
-        </is>
-      </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>-35,1</t>
+          <t>-23,09</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -1396,7 +1398,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>-29,35</t>
+          <t>-28,94</t>
         </is>
       </c>
     </row>
@@ -1409,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>-61,26; -34,51</t>
+          <t>-66,0; -39,38</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>-36,83; -7,0</t>
+          <t>-48,25; -19,18</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-66,73; -40,06</t>
+          <t>-61,01; -34,62</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>-49,03; -22,2</t>
+          <t>-36,33; -7,24</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-60,72; -42,25</t>
+          <t>-61,15; -41,92</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>-39,92; -18,13</t>
+          <t>-39,24; -18,05</t>
         </is>
       </c>
     </row>
@@ -1447,22 +1449,22 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>-71,32%</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>-44,77%</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
           <t>-73,12%</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>-34,38%</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>-71,32%</t>
-        </is>
-      </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>-45,78%</t>
+          <t>-34,58%</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -1472,7 +1474,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>-40,8%</t>
+          <t>-40,23%</t>
         </is>
       </c>
     </row>
@@ -1485,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>-84,02; -56,28</t>
+          <t>-81,93; -55,97</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>-51,54; -12,04</t>
+          <t>-59,1; -26,93</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-83,09; -55,99</t>
+          <t>-84,63; -57,13</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>-61,53; -31,41</t>
+          <t>-50,64; -11,48</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-79,89; -61,27</t>
+          <t>-80,34; -61,47</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>-52,65; -27,81</t>
+          <t>-52,31; -26,91</t>
         </is>
       </c>
     </row>
@@ -1527,22 +1529,22 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>-22,35</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>-55,16</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
           <t>-26,2</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>-44,99</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>-22,35</t>
-        </is>
-      </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>-54,56</t>
+          <t>-47,43</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -1552,7 +1554,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>-50,34</t>
+          <t>-51,58</t>
         </is>
       </c>
     </row>
@@ -1565,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-34,82; -16,43</t>
+          <t>-31,07; -12,65</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-54,6; -35,06</t>
+          <t>-63,19; -45,82</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-31,33; -12,86</t>
+          <t>-34,77; -16,36</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-62,29; -45,17</t>
+          <t>-56,21; -37,34</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>-30,64; -16,83</t>
+          <t>-30,77; -18,1</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>-56,75; -43,3</t>
+          <t>-57,43; -45,04</t>
         </is>
       </c>
     </row>
@@ -1603,22 +1605,22 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>-30,01%</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>-74,05%</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
           <t>-34,69%</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>-59,57%</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>-30,01%</t>
-        </is>
-      </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>-73,25%</t>
+          <t>-62,79%</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -1628,7 +1630,7 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>-67,13%</t>
+          <t>-68,78%</t>
         </is>
       </c>
     </row>
@@ -1641,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>-45,71; -23,87</t>
+          <t>-39,85; -17,78</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>-69,26; -48,29</t>
+          <t>-81,81; -64,88</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>-40,47; -18,15</t>
+          <t>-44,75; -23,36</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-80,93; -62,05</t>
+          <t>-70,81; -52,25</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>-39,52; -23,05</t>
+          <t>-39,74; -25,14</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>-73,87; -59,0</t>
+          <t>-74,57; -62,08</t>
         </is>
       </c>
     </row>
@@ -1683,22 +1685,22 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>22,04</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>50,42</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
           <t>12,58</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>42,69</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="inlineStr">
-        <is>
-          <t>22,04</t>
-        </is>
-      </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>50,07</t>
+          <t>43,06</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -1708,7 +1710,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>46,49</t>
+          <t>46,84</t>
         </is>
       </c>
     </row>
@@ -1721,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>4,04; 21,13</t>
+          <t>14,26; 30,6</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>35,72; 49,56</t>
+          <t>43,57; 56,76</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>12,9; 30,36</t>
+          <t>3,81; 20,65</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>42,92; 56,47</t>
+          <t>35,55; 49,83</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>10,66; 23,03</t>
+          <t>11,24; 23,24</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>40,99; 51,45</t>
+          <t>41,95; 51,49</t>
         </is>
       </c>
     </row>
@@ -1759,22 +1761,22 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>50,05%</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>114,5%</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
           <t>24,9%</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>84,53%</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="inlineStr">
-        <is>
-          <t>50,05%</t>
-        </is>
-      </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>113,7%</t>
+          <t>85,26%</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -1784,7 +1786,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>98,5%</t>
+          <t>99,24%</t>
         </is>
       </c>
     </row>
@@ -1797,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>7,76; 46,49</t>
+          <t>28,64; 77,75</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>64,33; 110,44</t>
+          <t>88,67; 150,31</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>27,22; 78,22</t>
+          <t>7,48; 45,67</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>86,18; 148,1</t>
+          <t>62,73; 110,59</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>21,7; 52,75</t>
+          <t>22,21; 53,29</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>79,68; 119,52</t>
+          <t>81,64; 119,7</t>
         </is>
       </c>
     </row>
@@ -1839,22 +1841,22 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>-9,09</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>-1,77</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
           <t>-12,62</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>-1,85</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>-9,09</t>
-        </is>
-      </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>-3,24</t>
+          <t>-1,98</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -1864,7 +1866,7 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>-2,63</t>
+          <t>-1,9</t>
         </is>
       </c>
     </row>
@@ -1877,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>-16,94; -8,03</t>
+          <t>-13,06; -4,8</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>-6,69; 4,45</t>
+          <t>-6,6; 2,81</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-13,31; -5,0</t>
+          <t>-16,72; -7,9</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>-8,57; 1,5</t>
+          <t>-6,42; 2,28</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-13,77; -7,92</t>
+          <t>-13,92; -7,73</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>-5,76; 1,24</t>
+          <t>-5,06; 1,36</t>
         </is>
       </c>
     </row>
@@ -1915,22 +1917,22 @@
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
+          <t>-14,69%</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>-2,87%</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
           <t>-19,61%</t>
         </is>
       </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>-2,87%</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>-14,69%</t>
-        </is>
-      </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>-5,24%</t>
+          <t>-3,07%</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -1940,7 +1942,7 @@
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>-4,18%</t>
+          <t>-3,01%</t>
         </is>
       </c>
     </row>
@@ -1953,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>-25,55; -12,95</t>
+          <t>-20,56; -8,01</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>-10,29; 6,93</t>
+          <t>-10,35; 4,63</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-20,81; -8,27</t>
+          <t>-25,27; -12,66</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>-13,79; 2,36</t>
+          <t>-9,59; 3,64</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-21,45; -12,79</t>
+          <t>-21,54; -12,49</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>-9,08; 1,99</t>
+          <t>-7,92; 2,21</t>
         </is>
       </c>
     </row>
